--- a/b1_b2_english_mandrin_curriculum.xlsx
+++ b/b1_b2_english_mandrin_curriculum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fd1bf83c93e14dd7/Projects/language_learning_channel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_C22A4D1CDD5ECF15C70DA9A1022948D510BCEEED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F433E9DF-91E4-4562-A5F5-083C7531AB01}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_C22A4D1CDD5ECF15C70DA9A1022948D510BCEEED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7870213D-276D-4234-A27D-A956F90A253B}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="-21600" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Curriculum" sheetId="1" r:id="rId1"/>
@@ -1418,9 +1418,9 @@
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="42" customWidth="1"/>
+    <col min="4" max="5" width="30" customWidth="1"/>
+    <col min="6" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1">
